--- a/offers/seasonal/عروض اليوم الوطني بيوديرما وسنسوداين.xlsx
+++ b/offers/seasonal/عروض اليوم الوطني بيوديرما وسنسوداين.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\9\عروض اليوم الوطني\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14036A1D-AF92-4839-810F-9C1CBAB86D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98A428D9-74C6-4817-87BF-AF824A26F5B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -101,6 +101,57 @@
   </si>
   <si>
     <t>خصم</t>
+  </si>
+  <si>
+    <t>00038758</t>
+  </si>
+  <si>
+    <t>00038759</t>
+  </si>
+  <si>
+    <t>00038760</t>
+  </si>
+  <si>
+    <t>00038761</t>
+  </si>
+  <si>
+    <t>00038762</t>
+  </si>
+  <si>
+    <t>00018369</t>
+  </si>
+  <si>
+    <t>0007322</t>
+  </si>
+  <si>
+    <t>00023346</t>
+  </si>
+  <si>
+    <t>00023347</t>
+  </si>
+  <si>
+    <t>00033991</t>
+  </si>
+  <si>
+    <t>0008083</t>
+  </si>
+  <si>
+    <t>00039248</t>
+  </si>
+  <si>
+    <t>0008036</t>
+  </si>
+  <si>
+    <t>00025034</t>
+  </si>
+  <si>
+    <t>00025033</t>
+  </si>
+  <si>
+    <t>0008111</t>
+  </si>
+  <si>
+    <t>00039249</t>
   </si>
 </sst>
 </file>
@@ -165,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -184,7 +235,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,14 +610,14 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <v>38758</v>
+      <c r="A2" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="3">
-        <v>141.44999999999999</v>
+        <v>157.16999999999999</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>12</v>
@@ -583,14 +633,14 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <v>38759</v>
+      <c r="A3" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="3">
-        <v>141.44999999999999</v>
+        <v>157.16999999999999</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>12</v>
@@ -606,14 +656,14 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <v>38760</v>
+      <c r="A4" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="3">
-        <v>141.44999999999999</v>
+        <v>157.16999999999999</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
@@ -629,14 +679,14 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <v>38761</v>
+      <c r="A5" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="3">
-        <v>141.44999999999999</v>
+        <v>157.16999999999999</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>12</v>
@@ -652,14 +702,14 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <v>38762</v>
+      <c r="A6" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="3">
-        <v>141.44999999999999</v>
+        <v>157.16999999999999</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>12</v>
@@ -675,8 +725,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>18369</v>
+      <c r="A7" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
@@ -685,7 +735,7 @@
         <v>31.9</v>
       </c>
       <c r="D7" s="3">
-        <v>23.924999999999997</v>
+        <v>23.93</v>
       </c>
       <c r="E7" s="4">
         <v>46295</v>
@@ -698,8 +748,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <v>7322</v>
+      <c r="A8" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -708,7 +758,7 @@
         <v>34.04</v>
       </c>
       <c r="D8" s="3">
-        <v>23.827999999999999</v>
+        <v>23.83</v>
       </c>
       <c r="E8" s="4">
         <v>46295</v>
@@ -721,8 +771,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <v>23346</v>
+      <c r="A9" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -731,7 +781,7 @@
         <v>39.79</v>
       </c>
       <c r="D9" s="3">
-        <v>31.832000000000001</v>
+        <v>31.83</v>
       </c>
       <c r="E9" s="4">
         <v>46295</v>
@@ -744,8 +794,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <v>23347</v>
+      <c r="A10" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
@@ -754,7 +804,7 @@
         <v>39.79</v>
       </c>
       <c r="D10" s="3">
-        <v>31.832000000000001</v>
+        <v>31.83</v>
       </c>
       <c r="E10" s="4">
         <v>46295</v>
@@ -767,8 +817,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <v>33991</v>
+      <c r="A11" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
@@ -790,8 +840,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8">
-        <v>8083</v>
+      <c r="A12" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>19</v>
@@ -800,7 +850,7 @@
         <v>49.15</v>
       </c>
       <c r="D12" s="3">
-        <v>36.862499999999997</v>
+        <v>36.86</v>
       </c>
       <c r="E12" s="4">
         <v>46295</v>
@@ -813,8 +863,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
-        <v>39248</v>
+      <c r="A13" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>20</v>
@@ -836,8 +886,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8">
-        <v>8036</v>
+      <c r="A14" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>21</v>
@@ -846,7 +896,7 @@
         <v>29.9</v>
       </c>
       <c r="D14" s="3">
-        <v>17.939999999999998</v>
+        <v>17.940000000000001</v>
       </c>
       <c r="E14" s="4">
         <v>46295</v>
@@ -859,8 +909,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <v>25034</v>
+      <c r="A15" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>22</v>
@@ -882,8 +932,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8">
-        <v>25033</v>
+      <c r="A16" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>23</v>
@@ -905,8 +955,8 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
-        <v>8111</v>
+      <c r="A17" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>24</v>
@@ -928,8 +978,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8">
-        <v>39249</v>
+      <c r="A18" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>25</v>
